--- a/aq_files/0084.xlsx
+++ b/aq_files/0084.xlsx
@@ -1,98 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>A company claims its average delivery time is 30 minutes. A researcher tests this claim using sample data. What statistical process is being used?</t>
-  </si>
-  <si>
-    <t>A researcher assumes a claim is true and tries to find evidence against it. What is this initial assumption called?</t>
-  </si>
-  <si>
-    <t>A hypothesis that represents no effect or no difference is called what?</t>
-  </si>
-  <si>
-    <t>A hypothesis that represents a change or effect is called what?</t>
-  </si>
-  <si>
-    <t>A researcher tests whether a new drug is more effective than an old one. Which hypothesis reflects this?</t>
-  </si>
-  <si>
-    <t>A company claims average salary is ₹50,000. What would be the null hypothesis?</t>
-  </si>
-  <si>
-    <t>A test is conducted to check whether a machine is producing correct weights. What is being tested?</t>
-  </si>
-  <si>
-    <t>Why is hypothesis testing important in decision-making?</t>
-  </si>
-  <si>
-    <t>A researcher rejects a claim based on sample data. What conclusion is made?</t>
-  </si>
-  <si>
-    <t>What does “statistical significance” mean?</t>
-  </si>
-  <si>
-    <t>Why do we use samples instead of entire populations?</t>
-  </si>
-  <si>
-    <t>What is the role of sample data in hypothesis testing?</t>
-  </si>
-  <si>
-    <t>What is meant by level of significance?</t>
-  </si>
-  <si>
-    <t>What does it mean to “fail to reject” a hypothesis?</t>
-  </si>
-  <si>
-    <t>A researcher compares sample results with a claim. What is this process?</t>
-  </si>
-  <si>
-    <t>What is a test statistic?</t>
-  </si>
-  <si>
-    <t>Why is randomness important in hypothesis testing?</t>
-  </si>
-  <si>
-    <t>What is the difference between assumption and conclusion in hypothesis testing?</t>
-  </si>
-  <si>
-    <t>Why can’t we prove a hypothesis absolutely?</t>
-  </si>
-  <si>
-    <t>What is inferential statistics in this context?</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -102,29 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -322,113 +316,963 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B51"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Order_ID,Order_Date,Order_Year,Order_Month,Order_Quarter,Customer_ID,Customer_Name,Customer_Age,Customer_Segment,Customer_State,Customer_City,Product_ID,Product_Name,Product_Category,Product_SubCategory,Unit_Price,Sales_Amount,Quantity,Discount,Profit,Shipping_Cost,Shipping_Days,Payment_Terms,Order_Priority,Delivery_Status,Return_Flag,Sales_Rep,Rep_Region</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1001,2024-01-05,2024,January,Q1,CUST-001,John Smith,45,Corporate,Illinois,Chicago,PROD-001,MacBook Pro,Electronics,Computers,1299.99,1299.99,1,0.05,389.99,15.00,3,Net30,High,Delivered,FALSE,Alice Johnson,North</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1002,2024-01-05,2024,January,Q1,CUST-001,John Smith,45,Corporate,Illinois,Chicago,PROD-002,Magic Mouse,Electronics,Accessories,79.99,79.99,3,0.10,23.99,8.50,2,Net30,Medium,Delivered,FALSE,Alice Johnson,North</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1003,2024-01-06,2024,January,Q1,CUST-002,Sarah Lee,28,Consumer,Texas,Houston,PROD-003,Designer Jeans,Clothing,Mens,44.99,89.99,2,0.00,26.99,12.00,4,COD,Medium,Delivered,FALSE,Bob Williams,South</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1004,2024-01-06,2024,January,Q1,CUST-003,Michael Brown,32,Consumer,Texas,Austin,PROD-004,27-inch Monitor,Electronics,Monitors,299.99,299.99,1,0.15,89.99,18.00,3,Net15,High,Delivered,FALSE,Bob Williams,South</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1005,2024-01-07,2024,January,Q1,CUST-004,Emily Davis,52,Corporate,New York,New York,PROD-005,Executive Chair,Furniture,Chairs,199.99,399.99,2,0.05,119.99,22.00,5,Net30,High,Delivered,FALSE,Carol Martinez,East</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1006,2024-01-07,2024,January,Q1,CUST-005,David Wilson,26,Consumer,New York,Buffalo,PROD-006,Mechanical Keyboard,Electronics,Keyboards,44.99,89.99,2,0.10,26.99,10.00,3,COD,Low,Delayed,FALSE,Carol Martinez,East</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1007,2024-01-08,2024,January,Q1,CUST-006,Lisa Anderson,34,Home Office,California,Los Angeles,PROD-007,Leather Jacket,Clothing,Womens,199.99,199.99,1,0.20,59.99,15.00,4,Net15,Medium,Delivered,FALSE,David Lee,West</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1008,2024-01-08,2024,January,Q1,CUST-007,Robert Taylor,41,Corporate,California,San Francisco,PROD-008,iPad,Electronics,Tablets,499.99,499.99,1,0.05,149.99,20.00,2,Net30,High,Delivered,FALSE,David Lee,West</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1009,2024-01-09,2024,January,Q1,CUST-008,Jennifer Martinez,38,Consumer,Illinois,Chicago,PROD-009,Floor Lamp,Furniture,Lighting,39.99,79.99,2,0.00,23.99,12.00,3,COD,Low,Delivered,FALSE,Alice Johnson,North</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1010,2024-01-09,2024,January,Q1,CUST-009,William Brown,29,Consumer,Michigan,Detroit,PROD-010,Running Shoes,Clothing,Mens,69.99,69.99,1,0.10,20.99,10.00,2,COD,Medium,Returned,TRUE,Alice Johnson,North</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1011,2024-01-10,2024,January,Q1,CUST-010,Patricia Davis,35,Corporate,Texas,Dallas,PROD-011,Gaming Laptop,Electronics,Computers,1299.99,1299.99,1,0.15,389.99,25.00,4,Net30,High,Delivered,FALSE,Bob Williams,South</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1012,2024-01-10,2024,January,Q1,CUST-011,Michael Miller,27,Consumer,Pennsylvania,Philadelphia,PROD-012,Headphones,Electronics,Audio,74.99,149.99,2,0.05,44.99,12.00,3,Net15,Medium,Delivered,FALSE,Carol Martinez,East</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1013,2024-01-11,2024,January,Q1,CUST-012,Linda Wilson,39,Home Office,California,San Diego,PROD-013,Wool Coat,Clothing,Womens,189.99,189.99,1,0.20,56.99,15.00,4,Net15,Medium,Delivered,FALSE,David Lee,West</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1014,2024-01-11,2024,January,Q1,CUST-013,Richard Moore,47,Corporate,Ohio,Columbus,PROD-014,Bookshelf,Furniture,Storage,159.99,159.99,1,0.10,47.99,18.00,5,Net30,Medium,Delivered,FALSE,Alice Johnson,North</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1015,2024-01-12,2024,January,Q1,CUST-014,Susan Taylor,31,Consumer,Florida,Miami,PROD-015,Smartphone,Electronics,Phones,349.99,699.99,2,0.05,209.99,12.00,3,COD,High,Delivered,FALSE,Bob Williams,South</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1016,2024-01-12,2024,January,Q1,CUST-015,Thomas Anderson,44,Corporate,New York,New York,PROD-016,Dress Shirt,Clothing,Mens,20.00,59.99,3,0.00,17.99,10.00,2,Net30,Medium,Delivered,FALSE,Carol Martinez,East</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1017,2024-01-13,2024,January,Q1,CUST-016,Jessica Thomas,33,Consumer,Oregon,Portland,PROD-017,External SSD,Electronics,Storage,99.99,99.99,1,0.10,29.99,8.50,3,COD,Low,Delivered,FALSE,David Lee,West</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1018,2024-01-13,2024,January,Q1,CUST-017,Charles Jackson,25,Consumer,Illinois,Chicago,PROD-018,Hoodie,Clothing,Womens,25.00,49.99,2,0.05,14.99,12.00,2,COD,Medium,Returned,TRUE,Alice Johnson,North</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1019,2024-01-14,2024,January,Q1,CUST-018,Sarah White,42,Corporate,Texas,Austin,PROD-019,Gaming Desk,Furniture,Desks,349.99,349.99,1,0.15,104.99,25.00,4,Net30,High,Delivered,FALSE,Bob Williams,South</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1020,2024-01-14,2024,January,Q1,CUST-019,Daniel Harris,36,Home Office,Massachusetts,Boston,PROD-020,Webcam,Electronics,Accessories,39.99,79.99,2,0.10,23.99,8.50,3,Net15,Medium,Delivered,FALSE,Carol Martinez,East</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1021,2024-02-01,2024,February,Q2,CUST-020,Matthew Clark,40,Consumer,Washington,Seattle,PROD-021,Docking Station,Electronics,Docks,129.99,129.99,1,0.00,38.99,10.00,3,COD,Low,Delivered,FALSE,David Lee,West</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1022,2024-02-01,2024,February,Q2,CUST-021,Amanda Lewis,48,Consumer,Minnesota,Minneapolis,PROD-022,Winter Parka,Clothing,Mens,179.99,179.99,1,0.05,53.99,15.00,4,COD,Medium,Delivered,FALSE,Alice Johnson,North</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1023,2024-02-02,2024,February,Q2,CUST-022,James Walker,53,Corporate,Florida,Orlando,PROD-023,Office Desk,Furniture,Desks,449.99,449.99,1,0.10,134.99,22.00,5,Net30,High,Delivered,FALSE,Bob Williams,South</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1024,2024-02-02,2024,February,Q2,CUST-023,Betty Hall,24,Consumer,New Jersey,Newark,PROD-024,USB-C Hub,Electronics,Cables,13.33,39.99,3,0.00,11.99,8.50,2,COD,Low,Delivered,FALSE,Carol Martinez,East</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1025,2024-02-03,2024,February,Q2,CUST-024,Kevin Young,37,Home Office,California,Los Angeles,PROD-025,Casual Blazer,Clothing,Mens,149.99,149.99,1,0.15,44.99,12.00,3,Net15,Medium,Delivered,FALSE,David Lee,West</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1026,2024-02-03,2024,February,Q2,CUST-025,Nancy Allen,22,Consumer,Indiana,Indianapolis,PROD-026,Gaming Mouse,Electronics,Accessories,29.99,59.99,2,0.10,17.99,8.50,2,COD,Medium,Returned,TRUE,Alice Johnson,North</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1027,2024-02-04,2024,February,Q2,CUST-026,Edward King,49,Corporate,Georgia,Atlanta,PROD-027,Laser Printer,Electronics,Printers,199.99,199.99,1,0.05,59.99,18.00,4,Net30,High,Delivered,FALSE,Bob Williams,South</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1028,2024-02-04,2024,February,Q2,CUST-027,Donna Wright,56,Consumer,Virginia,Richmond,PROD-028,Lounge Chair,Furniture,Chairs,279.99,279.99,1,0.20,83.99,22.00,5,Net15,Medium,Delivered,FALSE,Carol Martinez,East</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1029,2024-02-05,2024,February,Q2,CUST-028,George Lopez,30,Consumer,Arizona,Phoenix,PROD-029,Power Bank,Electronics,Batteries,12.50,49.99,4,0.00,14.99,8.50,2,COD,Low,Delivered,FALSE,David Lee,West</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1030,2024-02-05,2024,February,Q2,CUST-029,Sandra Hill,26,Consumer,Wisconsin,Milwaukee,PROD-030,Wool Scarf,Clothing,Accessories,5.00,24.99,5,0.10,7.49,8.50,2,COD,Medium,Delivered,FALSE,Alice Johnson,North</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1031,2024-02-06,2024,February,Q2,CUST-030,Brian Scott,34,Corporate,Texas,Houston,PROD-031,Gaming Headset,Electronics,Audio,119.99,119.99,1,0.05,35.99,12.00,3,Net30,High,Delivered,FALSE,Bob Williams,South</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1032,2024-02-06,2024,February,Q2,CUST-031,Carolyn Adams,44,Home Office,New York,Rochester,PROD-032,Night Stand,Furniture,Storage,34.99,69.99,2,0.10,20.99,15.00,3,Net15,Medium,Delivered,FALSE,Carol Martinez,East</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1033,2024-02-07,2024,February,Q2,CUST-032,Frank Baker,29,Consumer,California,San Jose,PROD-033,Athletic Shoes,Clothing,Mens,109.99,109.99,1,0.15,32.99,10.00,2,COD,Medium,Delivered,FALSE,David Lee,West</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1034,2024-02-07,2024,February,Q2,CUST-033,Ruth Gonzalez,38,Consumer,Missouri,St Louis,PROD-034,Smart Watch,Electronics,Wearables,199.99,199.99,1,0.05,59.99,12.00,3,Net15,High,Delivered,FALSE,Alice Johnson,North</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1035,2024-02-08,2024,February,Q2,CUST-034,Peter Nelson,31,Corporate,Florida,Tampa,PROD-035,Bluetooth Speaker,Electronics,Audio,39.99,79.99,2,0.10,23.99,10.00,3,Net30,Medium,Delivered,FALSE,Bob Williams,South</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1036,2024-02-08,2024,February,Q2,CUST-035,Kimberly Carter,41,Consumer,Pennsylvania,Pittsburgh,PROD-036,Cashmere Sweater,Clothing,Womens,99.99,99.99,1,0.00,29.99,12.00,3,COD,Low,Returned,TRUE,Carol Martinez,East</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1037,2024-02-09,2024,February,Q2,CUST-036,Steven Mitchell,46,Home Office,Oregon,Eugene,PROD-037,Bookshelf,Furniture,Storage,129.99,129.99,1,0.05,38.99,18.00,4,Net15,Medium,Delivered,FALSE,David Lee,West</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1038,2024-02-09,2024,February,Q2,CUST-037,Laura Perez,28,Consumer,Iowa,Des Moines,PROD-038,Mesh Router,Electronics,Networking,99.99,99.99,1,0.10,29.99,10.00,2,COD,Low,Delivered,FALSE,Alice Johnson,North</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1039,2024-02-10,2024,February,Q2,CUST-038,Paul Roberts,23,Consumer,Texas,San Antonio,PROD-039,Golf Polo,Clothing,Mens,15.00,44.99,3,0.15,13.49,8.50,2,COD,Medium,Delivered,FALSE,Bob Williams,South</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1040,2024-02-10,2024,February,Q2,CUST-039,Mary Turner,43,Corporate,Washington,Spokane,PROD-040,Graphics Card,Electronics,Components,499.99,499.99,1,0.20,149.99,18.00,4,Net30,High,Delivered,FALSE,David Lee,West</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1041,2024-03-01,2024,March,Q3,CUST-040,Daniel Phillips,50,Corporate,Illinois,Chicago,PROD-041,Desktop PC,Electronics,Computers,999.99,999.99,1,0.05,299.99,25.00,3,Net30,High,Delivered,FALSE,Alice Johnson,North</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1042,2024-03-01,2024,March,Q3,CUST-041,Lisa Campbell,27,Consumer,Texas,Austin,PROD-042,Yoga Pants,Clothing,Womens,25.00,49.99,2,0.00,14.99,8.50,2,COD,Medium,Delivered,FALSE,Bob Williams,South</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1043,2024-03-02,2024,March,Q3,CUST-042,Ronald Parker,55,Corporate,New York,New York,PROD-043,Coffee Table,Furniture,Tables,249.99,249.99,1,0.10,74.99,22.00,4,Net30,High,Delivered,FALSE,Carol Martinez,East</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1044,2024-03-02,2024,March,Q3,CUST-043,Deborah Evans,34,Home Office,California,Los Angeles,PROD-044,Smart Speaker,Electronics,Smart Home,45.00,89.99,2,0.00,26.99,10.00,2,Net15,Medium,Delivered,FALSE,David Lee,West</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1045,2024-03-03,2024,March,Q3,CUST-044,Joseph Edwards,19,Consumer,Michigan,Detroit,PROD-045,Baseball Cap,Clothing,Accessories,5.00,19.99,4,0.05,5.99,8.50,2,COD,Low,Delivered,FALSE,Alice Johnson,North</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1046,2024-03-03,2024,March,Q3,CUST-045,Barbara Collins,38,Consumer,Florida,Miami,PROD-046,Quadcopter,Electronics,Drones,349.99,349.99,1,0.10,104.99,18.00,3,COD,High,Delivered,FALSE,Bob Williams,South</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1047,2024-03-04,2024,March,Q3,CUST-046,Mark Stewart,42,Consumer,Pennsylvania,Philadelphia,PROD-047,Wall Mirror,Furniture,Decor,30.00,59.99,2,0.00,17.99,12.00,2,COD,Medium,Delivered,FALSE,Carol Martinez,East</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1048,2024-03-04,2024,March,Q3,CUST-047,Carol Morris,35,Home Office,Oregon,Portland,PROD-048,Flannel Shirt,Clothing,Mens,25.00,49.99,2,0.10,14.99,10.00,3,Net15,Medium,Delivered,FALSE,David Lee,West</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1049,2024-03-05,2024,March,Q3,CUST-048,Raymond Rogers,24,Consumer,Ohio,Columbus,PROD-049,Streaming Stick,Electronics,Streaming,10.00,29.99,3,0.05,8.99,8.50,2,COD,Low,Returned,TRUE,Alice Johnson,North</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>ORD-1050,2024-03-05,2024,March,Q3,CUST-049,Anna Reed,22,Consumer,Georgia,Atlanta,PROD-050,Leggings,Clothing,Womens,7.50,29.99,4,0.00,8.99,8.50,2,COD,Medium,Delivered,FALSE,Bob Williams,South</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>_Create Data Model</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>Create a Date table using CALENDAR function from the earliest to latest Order_Date in the dataset. What is the date range?</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr"/>
+      <c r="F2" s="0" t="inlineStr"/>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>_Create Data Model</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>Add calculated columns to the Date table: Year, Quarter Number, Month Number, Month Name, Weekday Name. How many columns are added?</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr"/>
+      <c r="F3" s="0" t="inlineStr"/>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>_Create Data Model</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>Create a relationship between Sales table Order_Date and Date table Date. What is the cardinality of this relationship?</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr"/>
+      <c r="F4" s="0" t="inlineStr"/>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>_Create Data Model</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>Create a Customer dimension table by extracting unique customers from the Sales table. How many unique customers are there?</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr"/>
+      <c r="F5" s="0" t="inlineStr"/>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>_Create Data Model</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>Create a Product dimension table with unique products. Include Product_ID, Product_Name, Product_Category, Product_SubCategory, Unit_Price. How many unique products?</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr"/>
+      <c r="F6" s="0" t="inlineStr"/>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>_Create Data Model</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>Create a relationship between Customer dimension and Sales fact table on Customer_ID. What type of relationship is this?</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr"/>
+      <c r="F7" s="0" t="inlineStr"/>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>_Create Data Model</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>Create a relationship between Product dimension and Sales fact table on Product_ID.</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr"/>
+      <c r="F8" s="0" t="inlineStr"/>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>_Create Data Model</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>Create a Sales Rep dimension table with unique sales representatives. How many sales reps are there?</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr"/>
+      <c r="F9" s="0" t="inlineStr"/>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>_Create Data Model</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>Create a hierarchy in the Date table: Year → Quarter → Month → Day. What are the levels in this hierarchy?</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr"/>
+      <c r="F10" s="0" t="inlineStr"/>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>_Create Data Model</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>Create a geography hierarchy: Customer_State → Customer_City in the Customer dimension table.</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr"/>
+      <c r="F11" s="0" t="inlineStr"/>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="n">
         <v>11</v>
       </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>_Create Data Model</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Create a product hierarchy: Product_Category → Product_SubCategory → Product_Name.</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr"/>
+      <c r="F12" s="0" t="inlineStr"/>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>_Create Data Model</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>Set the default summarization for numeric fields: Sales_Amount = Sum, Quantity = Sum, Profit = Sum, Discount = Average.</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr"/>
+      <c r="F13" s="0" t="inlineStr"/>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>_Create Data Model</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Mark the Date table as a date table for time intelligence functions. Select the Date column as the date column.</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="0" t="n">
         <v>14</v>
       </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>_Create Data Model</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Create a measure 'Total Sales' using SUM(Sales[Sales_Amount]) and format as currency with 2 decimals.</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr"/>
+      <c r="F15" s="0" t="inlineStr"/>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="0" t="n">
         <v>15</v>
       </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>_Create Data Model</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>Create a measure 'Total Profit' using SUM(Sales[Profit]) and 'Profit Margin' = DIVIDE([Total Profit], [Total Sales], 0) formatted as percentage.</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr"/>
+      <c r="F16" s="0" t="inlineStr"/>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="0" t="n">
         <v>16</v>
       </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>_Create Data Model</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>Create a measure 'Sales YTD' using TOTALYTD([Total Sales], DateTable[Date]). What is the YTD sales for March?</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr"/>
+      <c r="F17" s="0" t="inlineStr"/>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="0" t="n">
         <v>17</v>
       </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>_Create Data Model</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>Create a measure 'Sales Previous Month' using CALCULATE([Total Sales], PREVIOUSMONTH(DateTable[Date])). What are the sales for previous month?</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr"/>
+      <c r="F18" s="0" t="inlineStr"/>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="0" t="n">
         <v>18</v>
       </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>_Create Data Model</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>Create a measure 'Electronics Sales' using CALCULATE([Total Sales], Product[Product_Category] = 'Electronics'). What is the total electronics sales?</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr"/>
+      <c r="F19" s="0" t="inlineStr"/>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="0" t="n">
         <v>19</v>
       </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>_Create Data Model</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>Create a calculated column 'Customer Lifetime Value' in Customer table using CALCULATE(SUM(Sales[Sales_Amount]), RELATEDTABLE(Sales)).</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr"/>
+      <c r="F20" s="0" t="inlineStr"/>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>_Create Data Model</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Set row-level security roles for different regions: 'North_Region', 'South_Region', 'East_Region', 'West_Region' with DAX filters.</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr"/>
+      <c r="F21" s="0" t="inlineStr"/>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>